--- a/QuanLyHieuThuocTay/xuat_excel/Thong Ke Hoa Don Ngay 01-05-2026.xlsx
+++ b/QuanLyHieuThuocTay/xuat_excel/Thong Ke Hoa Don Ngay 01-05-2026.xlsx
@@ -6,13 +6,13 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="ThongKeNgay_01-05-2026" r:id="rId3" sheetId="1"/>
+    <sheet name="ChiTietNgay_01-05-2026" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Mã Hóa Đơn</t>
   </si>
@@ -35,10 +35,10 @@
     <t>HD001</t>
   </si>
   <si>
-    <t/>
+    <t>0961111111</t>
   </si>
   <si>
-    <t>Khách vãng lai</t>
+    <t>Nguyễn Thị Mai</t>
   </si>
   <si>
     <t>NV002</t>
@@ -47,19 +47,19 @@
     <t>Trần Thị Bình</t>
   </si>
   <si>
-    <t>45,750 VND</t>
+    <t>HD002</t>
   </si>
   <si>
-    <t>HD002</t>
+    <t/>
+  </si>
+  <si>
+    <t>Khách vãng lai</t>
   </si>
   <si>
     <t>NV003</t>
   </si>
   <si>
     <t>Lê Hoàng Cường</t>
-  </si>
-  <si>
-    <t>37,500 VND</t>
   </si>
 </sst>
 </file>
@@ -112,7 +112,7 @@
     <col min="3" max="3" width="15.41015625" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="13.7578125" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="15.7890625" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="11.6796875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="9.78515625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -151,28 +151,28 @@
       <c r="E2" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="F2" t="s" s="0">
-        <v>11</v>
+      <c r="F2" t="n" s="0">
+        <v>45750.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="B3" t="s" s="0">
-        <v>7</v>
-      </c>
       <c r="C3" t="s" s="0">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
-      <c r="F3" t="s" s="0">
-        <v>15</v>
+      <c r="F3" t="n" s="0">
+        <v>37500.0</v>
       </c>
     </row>
   </sheetData>
